--- a/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
+++ b/generated/spreadsheet/technical-details-consent-technical-details-consent.xlsx
@@ -808,7 +808,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Capacity unit</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the total capacity of a waste management facility</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Throughput unit</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the annual throughput of a waste management facility</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
